--- a/entregables/Renovacion_Contratos_FEE_ZBB.xlsx
+++ b/entregables/Renovacion_Contratos_FEE_ZBB.xlsx
@@ -18,11 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="$ #,##0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="167" formatCode="mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="mm/yyyy"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -187,7 +186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -249,7 +248,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -275,6 +274,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1202,10 +1204,10 @@
           <t>NOCTURNIDAD/EVENTOS</t>
         </is>
       </c>
-      <c r="I2" s="21" t="n">
+      <c r="I2" s="30" t="n">
         <v>45658</v>
       </c>
-      <c r="J2" s="21" t="n">
+      <c r="J2" s="30" t="n">
         <v>46388</v>
       </c>
       <c r="K2" s="22" t="n">
@@ -1303,10 +1305,10 @@
           <t>NOCTURNIDAD/EVENTOS</t>
         </is>
       </c>
-      <c r="I3" s="21" t="n">
+      <c r="I3" s="30" t="n">
         <v>45658</v>
       </c>
-      <c r="J3" s="21" t="n">
+      <c r="J3" s="30" t="n">
         <v>46388</v>
       </c>
       <c r="K3" s="22" t="n">
@@ -1404,10 +1406,10 @@
           <t>GASTRONOMIA</t>
         </is>
       </c>
-      <c r="I4" s="21" t="n">
+      <c r="I4" s="30" t="n">
         <v>45658</v>
       </c>
-      <c r="J4" s="21" t="n">
+      <c r="J4" s="30" t="n">
         <v>46388</v>
       </c>
       <c r="K4" s="22" t="n">
@@ -1505,10 +1507,10 @@
           <t>NOCTURNIDAD/EVENTOS</t>
         </is>
       </c>
-      <c r="I5" s="21" t="n">
+      <c r="I5" s="30" t="n">
         <v>45292</v>
       </c>
-      <c r="J5" s="21" t="n">
+      <c r="J5" s="30" t="n">
         <v>46388</v>
       </c>
       <c r="K5" s="22" t="n">
@@ -1606,10 +1608,10 @@
           <t>NOCTURNIDAD/EVENTOS</t>
         </is>
       </c>
-      <c r="I6" s="21" t="n">
+      <c r="I6" s="30" t="n">
         <v>45658</v>
       </c>
-      <c r="J6" s="21" t="n">
+      <c r="J6" s="30" t="n">
         <v>46388</v>
       </c>
       <c r="K6" s="22" t="n">
@@ -1707,10 +1709,10 @@
           <t>NOCTURNIDAD/EVENTOS</t>
         </is>
       </c>
-      <c r="I7" s="21" t="n">
+      <c r="I7" s="30" t="n">
         <v>45627</v>
       </c>
-      <c r="J7" s="21" t="n">
+      <c r="J7" s="30" t="n">
         <v>46357</v>
       </c>
       <c r="K7" s="22" t="n">
@@ -1808,10 +1810,10 @@
           <t>BALNEARIOS</t>
         </is>
       </c>
-      <c r="I8" s="21" t="n">
+      <c r="I8" s="30" t="n">
         <v>45658</v>
       </c>
-      <c r="J8" s="21" t="n">
+      <c r="J8" s="30" t="n">
         <v>46388</v>
       </c>
       <c r="K8" s="22" t="n">
@@ -1915,10 +1917,10 @@
           <t>GASTRONOMIA</t>
         </is>
       </c>
-      <c r="I9" s="21" t="n">
+      <c r="I9" s="30" t="n">
         <v>45658</v>
       </c>
-      <c r="J9" s="21" t="n">
+      <c r="J9" s="30" t="n">
         <v>46388</v>
       </c>
       <c r="K9" s="22" t="n">
@@ -2016,10 +2018,10 @@
           <t>NOCTURNIDAD/EVENTOS</t>
         </is>
       </c>
-      <c r="I10" s="21" t="n">
+      <c r="I10" s="30" t="n">
         <v>45292</v>
       </c>
-      <c r="J10" s="21" t="n">
+      <c r="J10" s="30" t="n">
         <v>46388</v>
       </c>
       <c r="K10" s="22" t="n">
@@ -2117,10 +2119,10 @@
           <t>GASTRONOMIA</t>
         </is>
       </c>
-      <c r="I11" s="21" t="n">
+      <c r="I11" s="30" t="n">
         <v>45658</v>
       </c>
-      <c r="J11" s="21" t="n">
+      <c r="J11" s="30" t="n">
         <v>46388</v>
       </c>
       <c r="K11" s="22" t="n">
@@ -2218,10 +2220,10 @@
           <t>NOCTURNIDAD/EVENTOS</t>
         </is>
       </c>
-      <c r="I12" s="21" t="n">
+      <c r="I12" s="30" t="n">
         <v>45658</v>
       </c>
-      <c r="J12" s="21" t="n">
+      <c r="J12" s="30" t="n">
         <v>46388</v>
       </c>
       <c r="K12" s="22" t="n">
@@ -2319,10 +2321,10 @@
           <t>OTROS</t>
         </is>
       </c>
-      <c r="I13" s="21" t="n">
+      <c r="I13" s="30" t="n">
         <v>45627</v>
       </c>
-      <c r="J13" s="21" t="n">
+      <c r="J13" s="30" t="n">
         <v>46357</v>
       </c>
       <c r="K13" s="22" t="n">
@@ -2420,10 +2422,10 @@
           <t>NOCTURNIDAD/EVENTOS</t>
         </is>
       </c>
-      <c r="I14" s="21" t="n">
+      <c r="I14" s="30" t="n">
         <v>45597</v>
       </c>
-      <c r="J14" s="21" t="n">
+      <c r="J14" s="30" t="n">
         <v>46327</v>
       </c>
       <c r="K14" s="22" t="n">
@@ -2521,10 +2523,10 @@
           <t>BALNEARIOS</t>
         </is>
       </c>
-      <c r="I15" s="21" t="n">
+      <c r="I15" s="30" t="n">
         <v>45292</v>
       </c>
-      <c r="J15" s="21" t="n">
+      <c r="J15" s="30" t="n">
         <v>46388</v>
       </c>
       <c r="K15" s="22" t="n">
@@ -2622,10 +2624,10 @@
           <t>GASTRONOMIA</t>
         </is>
       </c>
-      <c r="I16" s="21" t="n">
+      <c r="I16" s="30" t="n">
         <v>45658</v>
       </c>
-      <c r="J16" s="21" t="n">
+      <c r="J16" s="30" t="n">
         <v>46388</v>
       </c>
       <c r="K16" s="22" t="n">
@@ -2723,10 +2725,10 @@
           <t>GASTRONOMIA</t>
         </is>
       </c>
-      <c r="I17" s="21" t="n">
+      <c r="I17" s="30" t="n">
         <v>45658</v>
       </c>
-      <c r="J17" s="21" t="n">
+      <c r="J17" s="30" t="n">
         <v>46388</v>
       </c>
       <c r="K17" s="22" t="n">
@@ -2824,10 +2826,10 @@
           <t>GASTRONOMIA</t>
         </is>
       </c>
-      <c r="I18" s="21" t="n">
+      <c r="I18" s="30" t="n">
         <v>45778</v>
       </c>
-      <c r="J18" s="21" t="n">
+      <c r="J18" s="30" t="n">
         <v>46143</v>
       </c>
       <c r="K18" s="22" t="n">
@@ -2925,10 +2927,10 @@
           <t>BALNEARIOS</t>
         </is>
       </c>
-      <c r="I19" s="21" t="n">
+      <c r="I19" s="30" t="n">
         <v>45292</v>
       </c>
-      <c r="J19" s="21" t="n">
+      <c r="J19" s="30" t="n">
         <v>46388</v>
       </c>
       <c r="K19" s="22" t="n">
@@ -3026,10 +3028,10 @@
           <t>GASTRONOMIA</t>
         </is>
       </c>
-      <c r="I20" s="21" t="n">
+      <c r="I20" s="30" t="n">
         <v>45627</v>
       </c>
-      <c r="J20" s="21" t="n">
+      <c r="J20" s="30" t="n">
         <v>46357</v>
       </c>
       <c r="K20" s="22" t="n">
@@ -3133,10 +3135,10 @@
           <t>BALNEARIOS</t>
         </is>
       </c>
-      <c r="I21" s="21" t="n">
+      <c r="I21" s="30" t="n">
         <v>45597</v>
       </c>
-      <c r="J21" s="21" t="n">
+      <c r="J21" s="30" t="n">
         <v>46327</v>
       </c>
       <c r="K21" s="22" t="n">
@@ -3234,10 +3236,10 @@
           <t>GASTRONOMIA</t>
         </is>
       </c>
-      <c r="I22" s="21" t="n">
+      <c r="I22" s="30" t="n">
         <v>45658</v>
       </c>
-      <c r="J22" s="21" t="n">
+      <c r="J22" s="30" t="n">
         <v>46388</v>
       </c>
       <c r="K22" s="22" t="n">
@@ -3335,10 +3337,10 @@
           <t>GASTRONOMIA</t>
         </is>
       </c>
-      <c r="I23" s="21" t="n">
+      <c r="I23" s="30" t="n">
         <v>45627</v>
       </c>
-      <c r="J23" s="21" t="n">
+      <c r="J23" s="30" t="n">
         <v>46357</v>
       </c>
       <c r="K23" s="22" t="n">
@@ -3436,10 +3438,10 @@
           <t>GASTRONOMIA</t>
         </is>
       </c>
-      <c r="I24" s="21" t="n">
+      <c r="I24" s="30" t="n">
         <v>45536</v>
       </c>
-      <c r="J24" s="21" t="n">
+      <c r="J24" s="30" t="n">
         <v>46266</v>
       </c>
       <c r="K24" s="22" t="n">
@@ -3537,10 +3539,10 @@
           <t>BALNEARIOS</t>
         </is>
       </c>
-      <c r="I25" s="21" t="n">
+      <c r="I25" s="30" t="n">
         <v>45658</v>
       </c>
-      <c r="J25" s="21" t="n">
+      <c r="J25" s="30" t="n">
         <v>46388</v>
       </c>
       <c r="K25" s="22" t="n">
@@ -3638,10 +3640,10 @@
           <t>GASTRONOMIA</t>
         </is>
       </c>
-      <c r="I26" s="21" t="n">
+      <c r="I26" s="30" t="n">
         <v>45658</v>
       </c>
-      <c r="J26" s="21" t="n">
+      <c r="J26" s="30" t="n">
         <v>46388</v>
       </c>
       <c r="K26" s="22" t="n">
@@ -3739,10 +3741,10 @@
           <t>GASTRONOMIA</t>
         </is>
       </c>
-      <c r="I27" s="21" t="n">
+      <c r="I27" s="30" t="n">
         <v>45658</v>
       </c>
-      <c r="J27" s="21" t="n">
+      <c r="J27" s="30" t="n">
         <v>46388</v>
       </c>
       <c r="K27" s="22" t="n">
@@ -3840,10 +3842,10 @@
           <t>GASTRONOMIA</t>
         </is>
       </c>
-      <c r="I28" s="21" t="n">
+      <c r="I28" s="30" t="n">
         <v>45717</v>
       </c>
-      <c r="J28" s="21" t="n">
+      <c r="J28" s="30" t="n">
         <v>46357</v>
       </c>
       <c r="K28" s="22" t="n">
@@ -3945,10 +3947,10 @@
           <t>GASTRONOMIA</t>
         </is>
       </c>
-      <c r="I29" s="21" t="n">
+      <c r="I29" s="30" t="n">
         <v>45566</v>
       </c>
-      <c r="J29" s="21" t="n">
+      <c r="J29" s="30" t="n">
         <v>46296</v>
       </c>
       <c r="K29" s="22" t="n">
@@ -4046,10 +4048,10 @@
           <t>GASTRONOMIA</t>
         </is>
       </c>
-      <c r="I30" s="21" t="n">
+      <c r="I30" s="30" t="n">
         <v>45962</v>
       </c>
-      <c r="J30" s="21" t="n">
+      <c r="J30" s="30" t="n">
         <v>46327</v>
       </c>
       <c r="K30" s="22" t="n">
@@ -4153,10 +4155,10 @@
           <t>BALNEARIOS</t>
         </is>
       </c>
-      <c r="I31" s="21" t="n">
+      <c r="I31" s="30" t="n">
         <v>45658</v>
       </c>
-      <c r="J31" s="21" t="n">
+      <c r="J31" s="30" t="n">
         <v>46388</v>
       </c>
       <c r="K31" s="22" t="n">
